--- a/data/trans_dic/P56$pareja-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$pareja-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,16</t>
+          <t>0,0; 57,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,73; 75,89</t>
+          <t>24,36; 75,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 84,05</t>
+          <t>3,47; 83,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 34,43</t>
+          <t>4,37; 34,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,62</t>
+          <t>0,0; 51,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,05</t>
+          <t>0,0; 68,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 30,42</t>
+          <t>3,84; 33,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,35; 51,97</t>
+          <t>12,99; 52,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 40,91</t>
+          <t>1,38; 40,96</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,81</t>
+          <t>0,0; 71,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,73; 100,0</t>
+          <t>33,12; 92,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,26</t>
+          <t>0,0; 85,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,99; 71,22</t>
+          <t>14,63; 71,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,4</t>
+          <t>0,0; 43,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 29,77</t>
+          <t>2,97; 27,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,69</t>
+          <t>0,0; 26,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 24,63</t>
+          <t>7,28; 24,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 39,7</t>
+          <t>4,69; 39,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,55; 44,35</t>
+          <t>13,73; 41,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 33,5</t>
+          <t>4,12; 33,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,05; 30,13</t>
+          <t>12,84; 30,66</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,59; 91,27</t>
+          <t>25,69; 91,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,1; 85,96</t>
+          <t>12,21; 86,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,26; 53,83</t>
+          <t>20,66; 55,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 37,95</t>
+          <t>5,06; 37,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,47</t>
+          <t>0,0; 66,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 22,96</t>
+          <t>5,65; 21,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,68</t>
+          <t>0,0; 39,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 53,13</t>
+          <t>14,57; 51,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 57,87</t>
+          <t>9,57; 57,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,75; 30,47</t>
+          <t>13,37; 30,06</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,2; 87,8</t>
+          <t>22,62; 86,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,76; 91,58</t>
+          <t>35,83; 91,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,03; 70,79</t>
+          <t>23,68; 71,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,34</t>
+          <t>0,0; 44,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 39,66</t>
+          <t>5,06; 43,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,43</t>
+          <t>0,0; 30,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 16,48</t>
+          <t>2,04; 16,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,66</t>
+          <t>0,0; 37,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,87; 45,81</t>
+          <t>13,24; 45,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,59; 43,9</t>
+          <t>14,27; 45,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 30,17</t>
+          <t>9,21; 29,91</t>
         </is>
       </c>
     </row>
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,54</t>
+          <t>0,0; 38,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,95</t>
+          <t>0,0; 49,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,43</t>
+          <t>0,0; 20,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 53,35</t>
+          <t>7,39; 54,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 16,75</t>
+          <t>1,97; 16,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 56,99</t>
+          <t>6,36; 56,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,82</t>
+          <t>0,0; 27,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 54,56</t>
+          <t>7,21; 57,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 19,25</t>
+          <t>3,03; 18,4</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,88; 69,71</t>
+          <t>9,85; 67,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,7; 68,93</t>
+          <t>15,15; 68,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,24; 39,51</t>
+          <t>12,94; 39,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,69</t>
+          <t>0,0; 39,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,85</t>
+          <t>0,0; 31,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,89; 53,0</t>
+          <t>8,87; 51,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,87; 29,27</t>
+          <t>12,54; 30,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,35</t>
+          <t>0,0; 31,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,86; 34,67</t>
+          <t>6,87; 34,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,37; 48,34</t>
+          <t>13,83; 48,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,09; 29,37</t>
+          <t>14,07; 28,82</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,6; 84,54</t>
+          <t>15,83; 84,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,28; 75,2</t>
+          <t>18,49; 75,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,5; 65,14</t>
+          <t>21,2; 63,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,36; 52,8</t>
+          <t>11,7; 54,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,19; 34,77</t>
+          <t>6,7; 36,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,78; 31,15</t>
+          <t>7,13; 31,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,71; 35,21</t>
+          <t>16,36; 35,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,47; 59,36</t>
+          <t>8,76; 67,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,65; 40,56</t>
+          <t>14,31; 40,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,33; 37,44</t>
+          <t>14,82; 37,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,53; 36,45</t>
+          <t>17,52; 35,13</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,15; 66,76</t>
+          <t>22,57; 65,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,41</t>
+          <t>0,0; 71,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,77; 83,44</t>
+          <t>16,41; 83,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31,21; 65,07</t>
+          <t>31,66; 66,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,92; 38,1</t>
+          <t>8,17; 39,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,18; 36,85</t>
+          <t>7,31; 37,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,5; 21,7</t>
+          <t>8,34; 21,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,03; 43,62</t>
+          <t>16,86; 43,24</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,49; 35,45</t>
+          <t>8,56; 36,98</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 34,99</t>
+          <t>4,15; 33,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,48; 30,78</t>
+          <t>16,69; 29,98</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,42; 56,12</t>
+          <t>30,1; 57,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30,3; 55,11</t>
+          <t>30,14; 55,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36,82; 59,55</t>
+          <t>35,47; 57,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28,63; 44,67</t>
+          <t>29,15; 43,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,22; 19,31</t>
+          <t>5,82; 19,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,84; 20,17</t>
+          <t>9,93; 20,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,65; 20,57</t>
+          <t>8,57; 20,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,01; 17,96</t>
+          <t>11,77; 18,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,67; 28,44</t>
+          <t>15,68; 28,97</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17,51; 28,33</t>
+          <t>17,62; 28,11</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,6; 30,21</t>
+          <t>18,37; 29,7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,78; 24,13</t>
+          <t>17,54; 24,11</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2214,57 +2214,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4031</t>
+          <t>0; 4040</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2456; 7537</t>
+          <t>2420; 7517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>213; 4228</t>
+          <t>174; 4197</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1366</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>843; 7311</t>
+          <t>928; 7305</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8573</t>
+          <t>0; 9418</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 973</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4088</t>
+          <t>0; 4041</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1067; 8605</t>
+          <t>1085; 9382</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3782; 14718</t>
+          <t>3679; 14746</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>343; 5423</t>
+          <t>183; 5429</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4941</t>
+          <t>0; 4891</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4652; 11710</t>
+          <t>3879; 10823</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4731</t>
+          <t>0; 4709</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2561; 8689</t>
+          <t>1785; 8709</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6090</t>
+          <t>0; 6461</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1143; 10988</t>
+          <t>1095; 10152</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6003</t>
+          <t>0; 4713</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3388; 10323</t>
+          <t>3053; 10117</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1023; 8570</t>
+          <t>1012; 8506</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6587; 21560</t>
+          <t>6676; 20370</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>949; 7807</t>
+          <t>961; 7832</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6522; 16305</t>
+          <t>6950; 16596</t>
         </is>
       </c>
     </row>
@@ -2630,57 +2630,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2371; 8458</t>
+          <t>2381; 8460</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>727; 5167</t>
+          <t>734; 5180</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3710; 9858</t>
+          <t>3784; 10192</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>973; 7308</t>
+          <t>974; 7285</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6838</t>
+          <t>0; 7118</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2176; 7695</t>
+          <t>1892; 7267</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5570</t>
+          <t>0; 6016</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4203; 15153</t>
+          <t>4157; 14810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1572; 9713</t>
+          <t>1607; 9586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7127; 15791</t>
+          <t>6928; 15581</t>
         </is>
       </c>
     </row>
@@ -2838,57 +2838,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1146; 7625</t>
+          <t>1965; 7532</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3478; 9164</t>
+          <t>3586; 9165</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1766; 6566</t>
+          <t>2196; 6651</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3822</t>
+          <t>0; 4819</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1135; 8905</t>
+          <t>1136; 9831</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7335</t>
+          <t>0; 7667</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>402; 3258</t>
+          <t>404; 3319</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5848</t>
+          <t>0; 4965</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4318; 14265</t>
+          <t>4123; 14316</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4746; 15335</t>
+          <t>4986; 16024</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2795; 8763</t>
+          <t>2674; 8689</t>
         </is>
       </c>
     </row>
@@ -3051,52 +3051,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 616</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2891</t>
+          <t>0; 2912</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4374</t>
+          <t>0; 4463</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6192</t>
+          <t>0; 4048</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>894; 6463</t>
+          <t>895; 6653</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>326; 2778</t>
+          <t>327; 2662</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>856; 7533</t>
+          <t>841; 7438</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6818</t>
+          <t>0; 7298</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>902; 7045</t>
+          <t>931; 7449</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>841; 4636</t>
+          <t>731; 4432</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1336</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1052; 7424</t>
+          <t>1050; 7145</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1589; 7453</t>
+          <t>1638; 7410</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2188; 6530</t>
+          <t>2139; 6564</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4187</t>
+          <t>0; 4166</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6431</t>
+          <t>0; 6387</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1964; 11716</t>
+          <t>1961; 11456</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3770; 9297</t>
+          <t>3982; 9541</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4036</t>
+          <t>0; 4504</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2116; 10695</t>
+          <t>2119; 10589</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4731; 15913</t>
+          <t>4552; 15896</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6802; 14182</t>
+          <t>6795; 13915</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>809; 4385</t>
+          <t>821; 4371</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3154; 11695</t>
+          <t>2875; 11749</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4288; 12994</t>
+          <t>4228; 12672</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1409; 6551</t>
+          <t>1451; 6725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1433</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2191; 12318</t>
+          <t>2372; 12886</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2907; 13363</t>
+          <t>3058; 13637</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6587; 14763</t>
+          <t>6861; 15050</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>774; 5425</t>
+          <t>800; 6186</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6450; 20676</t>
+          <t>7297; 20630</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9007; 23530</t>
+          <t>9315; 23290</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9526; 19806</t>
+          <t>9518; 19087</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4447; 12826</t>
+          <t>4335; 12622</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6257</t>
+          <t>0; 6338</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1526; 7596</t>
+          <t>1494; 7617</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6492; 13537</t>
+          <t>6586; 13766</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2371; 11403</t>
+          <t>2444; 11734</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2157; 11078</t>
+          <t>2196; 11237</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2273</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4875; 12444</t>
+          <t>4781; 12186</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8862; 21438</t>
+          <t>8288; 21250</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3309; 13807</t>
+          <t>3332; 14404</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1502; 11149</t>
+          <t>1323; 10656</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>12877; 24047</t>
+          <t>13045; 23427</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>13721; 27095</t>
+          <t>14530; 27529</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>23790; 43266</t>
+          <t>23659; 43177</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26543; 42937</t>
+          <t>25572; 41326</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29216; 45587</t>
+          <t>29755; 44707</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5814; 18067</t>
+          <t>5442; 17941</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20190; 41405</t>
+          <t>20387; 42514</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14854; 35333</t>
+          <t>14730; 35472</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30139; 45077</t>
+          <t>29544; 46061</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22230; 40330</t>
+          <t>22241; 41080</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49691; 80387</t>
+          <t>49996; 79773</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45362; 73683</t>
+          <t>44807; 72443</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>62793; 85196</t>
+          <t>61941; 85141</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$pareja-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$pareja-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,3</t>
+          <t>0,0; 56,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,36; 75,68</t>
+          <t>20,75; 76,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 83,44</t>
+          <t>12,86; 85,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 34,4</t>
+          <t>4,37; 38,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,21</t>
+          <t>0,0; 52,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,26</t>
+          <t>0,0; 83,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 33,16</t>
+          <t>3,82; 32,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 52,07</t>
+          <t>13,1; 49,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 40,96</t>
+          <t>4,93; 38,26</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,09</t>
+          <t>0,0; 72,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,12; 92,43</t>
+          <t>39,73; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,85</t>
+          <t>0,0; 85,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,63; 71,38</t>
+          <t>20,92; 70,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,93</t>
+          <t>0,0; 47,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 27,51</t>
+          <t>3,05; 26,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,45</t>
+          <t>0,0; 33,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 24,13</t>
+          <t>6,88; 24,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 39,4</t>
+          <t>4,84; 40,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,73; 41,9</t>
+          <t>13,79; 42,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 33,61</t>
+          <t>4,22; 39,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,84; 30,66</t>
+          <t>13,3; 29,95</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,69; 91,29</t>
+          <t>25,62; 91,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,21; 86,17</t>
+          <t>11,81; 74,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,66; 55,66</t>
+          <t>20,66; 53,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 37,83</t>
+          <t>5,06; 37,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,07</t>
+          <t>0,0; 61,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 21,69</t>
+          <t>5,93; 22,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,62</t>
+          <t>0,0; 38,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,57; 51,92</t>
+          <t>14,52; 55,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,57; 57,11</t>
+          <t>9,55; 56,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,37; 30,06</t>
+          <t>13,51; 30,44</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,62; 86,72</t>
+          <t>12,53; 77,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,83; 91,59</t>
+          <t>34,18; 91,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,68; 71,7</t>
+          <t>19,21; 71,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,56</t>
+          <t>0,0; 38,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 43,78</t>
+          <t>5,27; 39,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,76</t>
+          <t>0,0; 26,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 16,78</t>
+          <t>2,05; 15,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,07</t>
+          <t>0,0; 41,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,24; 45,97</t>
+          <t>13,55; 45,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,27; 45,88</t>
+          <t>14,28; 44,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 29,91</t>
+          <t>9,14; 29,4</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,66</t>
+          <t>0,0; 69,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,82</t>
+          <t>0,0; 39,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,94</t>
+          <t>0,0; 44,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,55</t>
+          <t>0,0; 26,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 54,92</t>
+          <t>7,48; 61,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 16,05</t>
+          <t>1,92; 15,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 56,28</t>
+          <t>6,54; 58,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,64</t>
+          <t>0,0; 24,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 57,69</t>
+          <t>7,26; 59,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 18,4</t>
+          <t>2,98; 19,73</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 67,09</t>
+          <t>9,85; 60,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,15; 68,54</t>
+          <t>14,8; 63,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,94; 39,71</t>
+          <t>13,41; 41,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,5</t>
+          <t>0,0; 41,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,62</t>
+          <t>0,0; 31,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,87; 51,83</t>
+          <t>6,37; 51,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,54; 30,04</t>
+          <t>12,12; 29,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,64</t>
+          <t>0,0; 35,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 34,33</t>
+          <t>6,87; 34,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,83; 48,29</t>
+          <t>13,98; 49,17</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,07; 28,82</t>
+          <t>14,39; 29,33</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,83; 84,27</t>
+          <t>15,55; 84,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,49; 75,55</t>
+          <t>20,12; 79,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,2; 63,53</t>
+          <t>21,5; 66,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,7; 54,2</t>
+          <t>10,96; 55,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 36,37</t>
+          <t>6,01; 36,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,13; 31,79</t>
+          <t>7,36; 31,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,36; 35,9</t>
+          <t>15,55; 35,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,76; 67,68</t>
+          <t>8,66; 67,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,31; 40,47</t>
+          <t>14,39; 41,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,82; 37,06</t>
+          <t>15,53; 37,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,52; 35,13</t>
+          <t>17,38; 35,46</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -1697,32 +1697,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,57; 65,7</t>
+          <t>22,86; 66,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,33</t>
+          <t>0,0; 70,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,41; 83,67</t>
+          <t>16,32; 82,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31,66; 66,18</t>
+          <t>31,5; 64,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,17; 39,2</t>
+          <t>8,39; 39,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,31; 37,38</t>
+          <t>7,24; 37,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,27 +1732,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,34; 21,25</t>
+          <t>8,0; 21,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,86; 43,24</t>
+          <t>17,28; 43,61</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,56; 36,98</t>
+          <t>8,43; 35,26</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,15; 33,44</t>
+          <t>3,19; 32,17</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,69; 29,98</t>
+          <t>16,43; 30,98</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30,1; 57,02</t>
+          <t>27,88; 54,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30,14; 55,0</t>
+          <t>30,44; 55,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35,47; 57,32</t>
+          <t>37,16; 59,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29,15; 43,81</t>
+          <t>29,36; 44,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,82; 19,18</t>
+          <t>6,24; 20,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,93; 20,71</t>
+          <t>9,99; 20,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,57; 20,65</t>
+          <t>8,91; 20,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,77; 18,35</t>
+          <t>11,92; 18,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,68; 28,97</t>
+          <t>16,13; 29,62</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17,62; 28,11</t>
+          <t>16,66; 27,62</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,37; 29,7</t>
+          <t>18,48; 29,97</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,54; 24,11</t>
+          <t>18,01; 24,42</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>2280</t>
         </is>
       </c>
     </row>
@@ -2214,17 +2214,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4040</t>
+          <t>0; 4019</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2420; 7517</t>
+          <t>2061; 7601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>174; 4197</t>
+          <t>677; 4484</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>928; 7305</t>
+          <t>928; 8167</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 9418</t>
+          <t>0; 9646</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>0; 4945</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1085; 9382</t>
+          <t>1081; 9105</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3679; 14746</t>
+          <t>3710; 13915</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>183; 5429</t>
+          <t>676; 5249</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11080</t>
+          <t>12094</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4891</t>
+          <t>0; 4993</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3879; 10823</t>
+          <t>4652; 11710</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4709</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1785; 8709</t>
+          <t>2736; 9268</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6461</t>
+          <t>0; 6950</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1095; 10152</t>
+          <t>1124; 9924</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4713</t>
+          <t>0; 5971</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3053; 10117</t>
+          <t>3077; 10958</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1012; 8506</t>
+          <t>1045; 8806</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6676; 20370</t>
+          <t>6704; 20433</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>961; 7832</t>
+          <t>984; 9142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6950; 16596</t>
+          <t>7684; 17310</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>10842</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2381; 8460</t>
+          <t>2374; 8488</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>734; 5180</t>
+          <t>710; 4452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3784; 10192</t>
+          <t>3693; 9570</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>974; 7285</t>
+          <t>975; 7282</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7118</t>
+          <t>0; 6612</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1892; 7267</t>
+          <t>1990; 7531</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6016</t>
+          <t>0; 5868</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4157; 14810</t>
+          <t>4141; 15794</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1607; 9586</t>
+          <t>1604; 9527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6928; 15581</t>
+          <t>6948; 15654</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5493</t>
         </is>
       </c>
     </row>
@@ -2838,57 +2838,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1965; 7532</t>
+          <t>1088; 6741</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3586; 9165</t>
+          <t>3420; 9150</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2196; 6651</t>
+          <t>1829; 6781</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4819</t>
+          <t>0; 4164</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1136; 9831</t>
+          <t>1183; 8895</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7667</t>
+          <t>0; 6648</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>404; 3319</t>
+          <t>427; 3154</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4965</t>
+          <t>0; 5554</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4123; 14316</t>
+          <t>4220; 14190</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4986; 16024</t>
+          <t>4989; 15503</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2674; 8689</t>
+          <t>2773; 8919</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2070</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4537</t>
+          <t>0; 4644</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2912</t>
+          <t>0; 3062</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4463</t>
+          <t>0; 3974</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4048</t>
+          <t>0; 5133</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>895; 6653</t>
+          <t>906; 7448</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>327; 2662</t>
+          <t>331; 2753</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841; 7438</t>
+          <t>865; 7711</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 7298</t>
+          <t>0; 6380</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>931; 7449</t>
+          <t>937; 7735</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>731; 4432</t>
+          <t>743; 4913</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>10495</t>
         </is>
       </c>
     </row>
@@ -3254,57 +3254,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1050; 7145</t>
+          <t>1049; 6410</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1638; 7410</t>
+          <t>1600; 6829</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2139; 6564</t>
+          <t>2221; 6881</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4166</t>
+          <t>0; 4326</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6387</t>
+          <t>0; 6412</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1961; 11456</t>
+          <t>1409; 11278</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3982; 9541</t>
+          <t>3944; 9466</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4504</t>
+          <t>0; 4985</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2119; 10589</t>
+          <t>2119; 10677</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4552; 15896</t>
+          <t>4601; 16185</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6795; 13915</t>
+          <t>7065; 14405</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>17100</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>821; 4371</t>
+          <t>806; 4371</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2875; 11749</t>
+          <t>3129; 12430</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4228; 12672</t>
+          <t>4288; 13260</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1451; 6725</t>
+          <t>1634; 8336</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2372; 12886</t>
+          <t>2129; 12847</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3058; 13637</t>
+          <t>3159; 13683</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6861; 15050</t>
+          <t>8031; 18417</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>800; 6186</t>
+          <t>792; 6189</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7297; 20630</t>
+          <t>7335; 20942</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9315; 23290</t>
+          <t>9758; 23297</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9518; 19087</t>
+          <t>11563; 23593</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10057</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>9099</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>20708</t>
         </is>
       </c>
     </row>
@@ -3665,32 +3665,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4335; 12622</t>
+          <t>4392; 12847</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6338</t>
+          <t>0; 6248</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1494; 7617</t>
+          <t>1486; 7514</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6586; 13766</t>
+          <t>7465; 15358</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2444; 11734</t>
+          <t>2511; 11910</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2196; 11237</t>
+          <t>2176; 11161</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,27 +3700,27 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4781; 12186</t>
+          <t>5321; 14330</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8288; 21250</t>
+          <t>8492; 21432</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3332; 14404</t>
+          <t>3285; 13734</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1323; 10656</t>
+          <t>1016; 10251</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13045; 23427</t>
+          <t>14822; 27945</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36720</t>
+          <t>39743</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>36915</t>
+          <t>41340</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>73635</t>
+          <t>81083</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>14530; 27529</t>
+          <t>13462; 26214</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>23659; 43177</t>
+          <t>23900; 43723</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25572; 41326</t>
+          <t>26789; 43080</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29755; 44707</t>
+          <t>31882; 48288</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5442; 17941</t>
+          <t>5841; 19438</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20387; 42514</t>
+          <t>20512; 41476</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14730; 35472</t>
+          <t>15306; 35917</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>29544; 46061</t>
+          <t>32831; 50323</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22241; 41080</t>
+          <t>22875; 42002</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49996; 79773</t>
+          <t>47261; 78376</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44807; 72443</t>
+          <t>45064; 73099</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>61941; 85141</t>
+          <t>69153; 93755</t>
         </is>
       </c>
     </row>
